--- a/public/exports-from-60-with-coowners/29189668.xlsx
+++ b/public/exports-from-60-with-coowners/29189668.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">200017658</t>
+          <t xml:space="preserve">200017659</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8689,7 +8689,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215030</t>
+          <t xml:space="preserve">311215043</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -24814,7 +24814,7 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393677</t>
+          <t xml:space="preserve">311393687</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -27439,7 +27439,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27514,7 +27514,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -30889,7 +30889,7 @@
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424656</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -30964,7 +30964,7 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424656</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189668.xlsx
+++ b/public/exports-from-60-with-coowners/29189668.xlsx
@@ -8764,7 +8764,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215051</t>
+          <t xml:space="preserve">311215030</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -26839,7 +26839,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -26914,7 +26914,7 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -26989,7 +26989,7 @@
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -27139,7 +27139,7 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -30364,7 +30364,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424656</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424656</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -38614,7 +38614,7 @@
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
@@ -38689,7 +38689,7 @@
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -38764,7 +38764,7 @@
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -38839,7 +38839,7 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
